--- a/项目唯一代码.xlsx
+++ b/项目唯一代码.xlsx
@@ -32,10 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="0."/>
-    <numFmt numFmtId="165" formatCode="¥0,0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -399,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B5"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -415,231 +413,39 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>红沿河三期</v>
+        <v>胜利油田芳庄设备项目</v>
       </c>
       <c r="B2" t="str">
-        <v>PT6G</v>
+        <v>ZSO8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>锦州石化2026年</v>
+        <v>陕煤IT运维项目</v>
       </c>
       <c r="B3" t="str">
-        <v>POTL</v>
+        <v>OKIB</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>胜利油田芳庄设备项目</v>
+        <v>煤层综采工作面AI大模型</v>
       </c>
       <c r="B4" t="str">
-        <v>ZSO8</v>
+        <v>EJOL</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>胜利油田AI大模型项目</v>
+        <v>哈动装核主泵项目</v>
       </c>
       <c r="B5" t="str">
-        <v>B16F</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026年科研项目A</v>
-      </c>
-      <c r="B6" t="str">
-        <v>EA2O</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2026年科研项目B</v>
-      </c>
-      <c r="B7" t="str">
-        <v>77P8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>哈动装算法代码项目</v>
-      </c>
-      <c r="B8" t="str">
-        <v>6PP3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>硝化棉产线标配项目</v>
-      </c>
-      <c r="B9" t="str">
-        <v>YY0B</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>天普纤维素二期</v>
-      </c>
-      <c r="B10" t="str">
-        <v>RRSB</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>天普纤维素新建产线</v>
-      </c>
-      <c r="B11" t="str">
-        <v>0WB7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>24T项目</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2OJS</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>北化575项目931工房</v>
-      </c>
-      <c r="B13" t="str">
-        <v>4IUV</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>北化科研项目</v>
-      </c>
-      <c r="B14" t="str">
-        <v>XP8J</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>陕煤IT运维项目</v>
-      </c>
-      <c r="B15" t="str">
-        <v>OKIB</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>陕煤智能会议系统</v>
-      </c>
-      <c r="B16" t="str">
-        <v>JJWA</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>硬件采购</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Q3CW</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>泸州北化二期项目-2</v>
-      </c>
-      <c r="B18" t="str">
-        <v>09GE</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>哈动装核主泵项目</v>
-      </c>
-      <c r="B19" t="str">
         <v>QL0X</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>泸州北化255项目</v>
-      </c>
-      <c r="B20" t="str">
-        <v>R24R</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>天普纤维素项目5支定制款V02</v>
-      </c>
-      <c r="B21" t="str">
-        <v>LPTQ</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>锦州石化2025年第二期</v>
-      </c>
-      <c r="B22" t="str">
-        <v>JO6U</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>重庆水泵项目</v>
-      </c>
-      <c r="B23" t="str">
-        <v>X3TN</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>鑫达钢铁项目</v>
-      </c>
-      <c r="B24" t="str">
-        <v>U3CC</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>高义钢铁二期项目</v>
-      </c>
-      <c r="B25" t="str">
-        <v>36UA</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>锦州石化2025年第一期</v>
-      </c>
-      <c r="B26" t="str">
-        <v>N6SQ</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>泸州北化二期项目</v>
-      </c>
-      <c r="B27" t="str">
-        <v>O8VJ</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>红沿河三期</v>
-      </c>
-      <c r="B28" t="str">
-        <v>APXI</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>高义钢铁项目</v>
-      </c>
-      <c r="B29" t="str">
-        <v>BD64</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/项目唯一代码.xlsx
+++ b/项目唯一代码.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -413,39 +413,87 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>胜利油田芳庄设备项目</v>
+        <v>2026年科研项目A</v>
       </c>
       <c r="B2" t="str">
-        <v>ZSO8</v>
+        <v>EA2O</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>陕煤IT运维项目</v>
+        <v>2026年科研项目B</v>
       </c>
       <c r="B3" t="str">
-        <v>OKIB</v>
+        <v>77P8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>煤层综采工作面AI大模型</v>
+        <v>硝化棉产线标配项目</v>
       </c>
       <c r="B4" t="str">
-        <v>EJOL</v>
+        <v>YY0B</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>哈动装核主泵项目</v>
+        <v>天普纤维素二期</v>
       </c>
       <c r="B5" t="str">
-        <v>QL0X</v>
+        <v>RRSB</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>天普纤维素新建产线</v>
+      </c>
+      <c r="B6" t="str">
+        <v>0WB7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>陕煤智能会议系统</v>
+      </c>
+      <c r="B7" t="str">
+        <v>JJWA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>煤层综采工作面AI大模型</v>
+      </c>
+      <c r="B8" t="str">
+        <v>EJOL</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>泸州北化二期项目-2</v>
+      </c>
+      <c r="B9" t="str">
+        <v>09GE</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>泸州北化255项目</v>
+      </c>
+      <c r="B10" t="str">
+        <v>R24R</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>四川财经学院</v>
+      </c>
+      <c r="B11" t="str">
+        <v>THT2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>